--- a/data/source/PRESTAMOS_AL_SECTOR_AGRO_2025.xlsx
+++ b/data/source/PRESTAMOS_AL_SECTOR_AGRO_2025.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ciro_\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FD2234-9729-40E9-AA75-05FB2D7C8684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B82F296-C794-45DF-9053-B52C68BF5344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{EA50B348-1142-44F2-825B-C9E3B06DD6D2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{EA50B348-1142-44F2-825B-C9E3B06DD6D2}"/>
   </bookViews>
   <sheets>
     <sheet name="2025 - SALDOS" sheetId="1" r:id="rId1"/>
     <sheet name="2025 - TASAS" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2025 - TASAS'!$A$1:$AB$69</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="42">
   <si>
     <t>ACTIVIDAD</t>
   </si>
@@ -161,9 +164,6 @@
   </si>
   <si>
     <t>PERIODO</t>
-  </si>
-  <si>
-    <t>TASAS</t>
   </si>
 </sst>
 </file>
@@ -11259,7 +11259,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9FDA6BC-042C-4BA2-82BB-F83056CF6811}">
-  <dimension ref="A1:AB69"/>
+  <dimension ref="A1:AB81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -11273,7 +11273,7 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E1" t="s">
         <v>16</v>
@@ -13479,351 +13479,333 @@
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B30">
         <v>20250630</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>7.36</v>
+        <v>49.63</v>
       </c>
       <c r="E30">
-        <v>7.26</v>
+        <v>38.79</v>
       </c>
       <c r="F30">
-        <v>7.64</v>
+        <v>55.55</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>78.760000000000005</v>
       </c>
       <c r="H30">
-        <v>8.58</v>
+        <v>59.15</v>
       </c>
       <c r="I30">
-        <v>10.26</v>
+        <v>67.2</v>
       </c>
       <c r="J30">
-        <v>7.64</v>
+        <v>29.01</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="L30">
-        <v>7.32</v>
+        <v>46.09</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>51.05</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>38.99</v>
       </c>
       <c r="O30">
-        <v>8.42</v>
+        <v>58.62</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="Q30">
-        <v>8.11</v>
-      </c>
-      <c r="R30">
-        <v>7.79</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
+        <v>67.84</v>
       </c>
       <c r="T30">
-        <v>9.44</v>
+        <v>43.41</v>
       </c>
       <c r="U30">
-        <v>8.61</v>
+        <v>76.95</v>
       </c>
       <c r="V30">
-        <v>7.69</v>
+        <v>75.58</v>
       </c>
       <c r="W30">
-        <v>12</v>
-      </c>
-      <c r="X30">
-        <v>0</v>
+        <v>71.25</v>
       </c>
       <c r="Y30">
-        <v>5.34</v>
+        <v>55.2</v>
       </c>
       <c r="Z30">
-        <v>8.1</v>
+        <v>84.71</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB30">
-        <v>8.57</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B31">
         <v>20250630</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>6.6</v>
+        <v>47.75</v>
       </c>
       <c r="E31">
-        <v>6.15</v>
+        <v>48.05</v>
       </c>
       <c r="F31">
-        <v>6.42</v>
+        <v>47.65</v>
       </c>
       <c r="G31">
-        <v>7</v>
+        <v>46.03</v>
       </c>
       <c r="H31">
-        <v>9.75</v>
+        <v>48.83</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>50.46</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>49.49</v>
       </c>
       <c r="K31">
-        <v>15</v>
+        <v>39.9</v>
       </c>
       <c r="L31">
-        <v>2.93</v>
+        <v>39.08</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>52.99</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>41.66</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>44.72</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>44.16</v>
       </c>
       <c r="Q31">
-        <v>6.73</v>
+        <v>42.23</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>44.73</v>
       </c>
       <c r="S31">
-        <v>6.9</v>
+        <v>48.14</v>
       </c>
       <c r="T31">
-        <v>7.57</v>
+        <v>49.82</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>57.62</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>58.35</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>54.56</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>58.56</v>
       </c>
       <c r="Y31">
-        <v>5.33</v>
+        <v>50.93</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>59.08</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>46.55</v>
       </c>
       <c r="AB31">
-        <v>6.77</v>
+        <v>54.93</v>
       </c>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B32">
         <v>20250630</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32">
-        <v>7.16</v>
+        <v>42.17</v>
       </c>
       <c r="E32">
-        <v>7.2</v>
+        <v>42.47</v>
       </c>
       <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
+        <v>42.64</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>62.01</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>43.02</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>59.75</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>32.369999999999997</v>
       </c>
       <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
+        <v>68.5</v>
       </c>
       <c r="P32">
-        <v>6.5</v>
+        <v>36.5</v>
       </c>
       <c r="Q32">
-        <v>7.15</v>
+        <v>52.99</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>35.5</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>65.62</v>
       </c>
       <c r="T32">
-        <v>7.12</v>
+        <v>48.25</v>
       </c>
       <c r="U32">
-        <v>8.6999999999999993</v>
+        <v>46.95</v>
       </c>
       <c r="V32">
-        <v>6.27</v>
+        <v>81.59</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>59.56</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>38.01</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>43.4</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>54.06</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>53.37</v>
       </c>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B33">
         <v>20250630</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>6.17</v>
+        <v>47.04</v>
       </c>
       <c r="E33">
-        <v>6.04</v>
+        <v>49.03</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>48.15</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>39.83</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>39.26</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>49.87</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>60.62</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>76.59</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>46.16</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>74.739999999999995</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>38.14</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>48.67</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>88.58</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>50.75</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>45.61</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>70.680000000000007</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>45.28</v>
       </c>
       <c r="U33">
-        <v>6.75</v>
+        <v>43.5</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>85.61</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>46.82</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>75.31</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>43.12</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>46.78</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>42.66</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>42.81</v>
       </c>
     </row>
     <row r="34" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B34">
         <v>20250630</v>
@@ -13832,31 +13814,31 @@
         <v>2</v>
       </c>
       <c r="D34">
+        <v>7.36</v>
+      </c>
+      <c r="E34">
+        <v>7.26</v>
+      </c>
+      <c r="F34">
         <v>7.64</v>
       </c>
-      <c r="E34">
-        <v>7.5</v>
-      </c>
-      <c r="F34">
-        <v>7.59</v>
-      </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34">
-        <v>9.5</v>
+        <v>8.58</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>10.26</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>7.64</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>7.77</v>
+        <v>7.32</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -13865,51 +13847,51 @@
         <v>0</v>
       </c>
       <c r="O34">
-        <v>3</v>
+        <v>8.42</v>
       </c>
       <c r="P34">
         <v>0</v>
       </c>
       <c r="Q34">
-        <v>6.59</v>
+        <v>8.11</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>7.79</v>
       </c>
       <c r="S34">
         <v>0</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>9.44</v>
       </c>
       <c r="U34">
-        <v>7.94</v>
+        <v>8.61</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="X34">
         <v>0</v>
       </c>
       <c r="Y34">
-        <v>5.72</v>
+        <v>5.34</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA34">
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>8.06</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="35" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B35">
         <v>20250630</v>
@@ -13918,19 +13900,19 @@
         <v>2</v>
       </c>
       <c r="D35">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="F35">
-        <v>7.5</v>
+        <v>6.42</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -13939,10 +13921,10 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -13957,16 +13939,16 @@
         <v>0</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="R35">
         <v>0</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>7.57</v>
       </c>
       <c r="U35">
         <v>0</v>
@@ -13981,7 +13963,7 @@
         <v>0</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -13990,12 +13972,12 @@
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="36" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B36">
         <v>20250630</v>
@@ -14004,19 +13986,19 @@
         <v>2</v>
       </c>
       <c r="D36">
-        <v>9.52</v>
+        <v>7.16</v>
       </c>
       <c r="E36">
-        <v>8.23</v>
+        <v>7.2</v>
       </c>
       <c r="F36">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G36">
         <v>0</v>
       </c>
       <c r="H36">
-        <v>10.09</v>
+        <v>0</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -14040,10 +14022,10 @@
         <v>0</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -14052,13 +14034,13 @@
         <v>0</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>7.12</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>6.27</v>
       </c>
       <c r="W36">
         <v>0</v>
@@ -14081,7 +14063,7 @@
     </row>
     <row r="37" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B37">
         <v>20250630</v>
@@ -14090,19 +14072,19 @@
         <v>2</v>
       </c>
       <c r="D37">
-        <v>7.71</v>
+        <v>6.17</v>
       </c>
       <c r="E37">
-        <v>7.32</v>
+        <v>6.04</v>
       </c>
       <c r="F37">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37">
-        <v>7.97</v>
+        <v>0</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -14141,7 +14123,7 @@
         <v>0</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="V37">
         <v>0</v>
@@ -14153,7 +14135,7 @@
         <v>0</v>
       </c>
       <c r="Y37">
-        <v>8.2899999999999991</v>
+        <v>0</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -14167,306 +14149,351 @@
     </row>
     <row r="38" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38">
+        <v>20250630</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38">
+        <v>7.64</v>
+      </c>
+      <c r="E38">
+        <v>7.5</v>
+      </c>
+      <c r="F38">
+        <v>7.59</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>9.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>7.77</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
         <v>3</v>
       </c>
-      <c r="B38">
-        <v>20250930</v>
-      </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38">
-        <v>76.14</v>
-      </c>
-      <c r="E38">
-        <v>84.75</v>
-      </c>
-      <c r="F38">
-        <v>75.5</v>
-      </c>
-      <c r="G38">
-        <v>77.52</v>
-      </c>
-      <c r="H38">
-        <v>72.08</v>
-      </c>
-      <c r="I38">
-        <v>66.39</v>
-      </c>
-      <c r="J38">
-        <v>56.23</v>
-      </c>
-      <c r="K38">
-        <v>87.76</v>
-      </c>
-      <c r="L38">
-        <v>65.91</v>
-      </c>
-      <c r="M38">
-        <v>81.41</v>
-      </c>
-      <c r="N38">
-        <v>79.48</v>
-      </c>
-      <c r="O38">
-        <v>88.57</v>
-      </c>
       <c r="P38">
-        <v>68.19</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>77.02</v>
+        <v>6.59</v>
       </c>
       <c r="R38">
-        <v>62.27</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>68.13</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>78.37</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>83.41</v>
+        <v>7.94</v>
       </c>
       <c r="V38">
-        <v>82.11</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>68.290000000000006</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>96.16</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>68.53</v>
+        <v>5.72</v>
       </c>
       <c r="Z38">
-        <v>73.33</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>108.02</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>75.87</v>
+        <v>8.06</v>
       </c>
     </row>
     <row r="39" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B39">
-        <v>20250930</v>
+        <v>20250630</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39">
-        <v>104.13</v>
+        <v>7.5</v>
       </c>
       <c r="E39">
-        <v>113.02</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>74.75</v>
+        <v>7.5</v>
       </c>
       <c r="G39">
-        <v>90.76</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>92.64</v>
+        <v>0</v>
       </c>
       <c r="I39">
-        <v>59.5</v>
+        <v>0</v>
       </c>
       <c r="J39">
-        <v>83.68</v>
+        <v>0</v>
       </c>
       <c r="K39">
-        <v>78.239999999999995</v>
+        <v>0</v>
       </c>
       <c r="L39">
-        <v>78.790000000000006</v>
+        <v>0</v>
       </c>
       <c r="M39">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="N39">
-        <v>71.47</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>87.72</v>
+        <v>0</v>
       </c>
       <c r="P39">
-        <v>91.47</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>95.78</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>79.31</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>62.28</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>76.930000000000007</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>86.13</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>87.61</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>77.66</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>89.46</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>81.540000000000006</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>89.33</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>117.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B40">
-        <v>20250930</v>
+        <v>20250630</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40">
-        <v>78.489999999999995</v>
+        <v>9.52</v>
       </c>
       <c r="E40">
-        <v>75.709999999999994</v>
+        <v>8.23</v>
       </c>
       <c r="F40">
-        <v>106.04</v>
+        <v>6</v>
       </c>
       <c r="G40">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <v>98.35</v>
+        <v>10.09</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
       </c>
       <c r="J40">
-        <v>63.91</v>
+        <v>0</v>
       </c>
       <c r="K40">
-        <v>73.02</v>
+        <v>0</v>
       </c>
       <c r="L40">
-        <v>82.79</v>
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>94.36</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>75.150000000000006</v>
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>88.88</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>87.74</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>84.55</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>86.28</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>78.25</v>
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>114.46</v>
+        <v>0</v>
       </c>
       <c r="Z40">
-        <v>85</v>
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B41">
-        <v>20250930</v>
+        <v>20250630</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41">
-        <v>78.510000000000005</v>
+        <v>7.71</v>
       </c>
       <c r="E41">
-        <v>69.89</v>
+        <v>7.32</v>
       </c>
       <c r="F41">
-        <v>72.099999999999994</v>
+        <v>5.45</v>
       </c>
       <c r="G41">
-        <v>83.15</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>107.29</v>
+        <v>7.97</v>
       </c>
       <c r="I41">
-        <v>86.32</v>
+        <v>0</v>
       </c>
       <c r="J41">
-        <v>65.760000000000005</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="L41">
-        <v>89</v>
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
       </c>
       <c r="N41">
-        <v>78.67</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>86</v>
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>89.01</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>85.13</v>
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
       </c>
       <c r="T41">
-        <v>86.26</v>
+        <v>0</v>
       </c>
       <c r="U41">
-        <v>76.19</v>
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
       </c>
       <c r="W41">
-        <v>96.18</v>
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
       </c>
       <c r="AA41">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="AB41">
-        <v>80.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B42">
         <v>20250930</v>
@@ -14475,84 +14502,84 @@
         <v>1</v>
       </c>
       <c r="D42">
-        <v>75.64</v>
+        <v>76.14</v>
       </c>
       <c r="E42">
-        <v>71.709999999999994</v>
+        <v>84.75</v>
       </c>
       <c r="F42">
-        <v>75.650000000000006</v>
+        <v>75.5</v>
       </c>
       <c r="G42">
-        <v>72.55</v>
+        <v>77.52</v>
       </c>
       <c r="H42">
-        <v>74.42</v>
+        <v>72.08</v>
       </c>
       <c r="I42">
-        <v>88.88</v>
+        <v>66.39</v>
       </c>
       <c r="J42">
-        <v>68.819999999999993</v>
+        <v>56.23</v>
       </c>
       <c r="K42">
-        <v>88.39</v>
+        <v>87.76</v>
       </c>
       <c r="L42">
-        <v>72.760000000000005</v>
+        <v>65.91</v>
       </c>
       <c r="M42">
-        <v>74.150000000000006</v>
+        <v>81.41</v>
       </c>
       <c r="N42">
-        <v>89</v>
+        <v>79.48</v>
       </c>
       <c r="O42">
-        <v>74.77</v>
+        <v>88.57</v>
       </c>
       <c r="P42">
-        <v>98.02</v>
+        <v>68.19</v>
       </c>
       <c r="Q42">
-        <v>80.900000000000006</v>
+        <v>77.02</v>
       </c>
       <c r="R42">
-        <v>84.63</v>
+        <v>62.27</v>
       </c>
       <c r="S42">
-        <v>83.27</v>
+        <v>68.13</v>
       </c>
       <c r="T42">
-        <v>89.73</v>
+        <v>78.37</v>
       </c>
       <c r="U42">
-        <v>75.989999999999995</v>
+        <v>83.41</v>
       </c>
       <c r="V42">
-        <v>72.89</v>
+        <v>82.11</v>
       </c>
       <c r="W42">
-        <v>65.55</v>
+        <v>68.290000000000006</v>
       </c>
       <c r="X42">
-        <v>85.46</v>
+        <v>96.16</v>
       </c>
       <c r="Y42">
-        <v>77.3</v>
+        <v>68.53</v>
       </c>
       <c r="Z42">
-        <v>85.46</v>
+        <v>73.33</v>
       </c>
       <c r="AA42">
-        <v>86</v>
+        <v>108.02</v>
       </c>
       <c r="AB42">
-        <v>71.45</v>
+        <v>75.87</v>
       </c>
     </row>
     <row r="43" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B43">
         <v>20250930</v>
@@ -14561,57 +14588,84 @@
         <v>1</v>
       </c>
       <c r="D43">
-        <v>78.37</v>
+        <v>104.13</v>
       </c>
       <c r="E43">
-        <v>44.61</v>
+        <v>113.02</v>
       </c>
       <c r="F43">
-        <v>79.34</v>
+        <v>74.75</v>
+      </c>
+      <c r="G43">
+        <v>90.76</v>
       </c>
       <c r="H43">
-        <v>60.2</v>
+        <v>92.64</v>
       </c>
       <c r="I43">
-        <v>75.510000000000005</v>
+        <v>59.5</v>
       </c>
       <c r="J43">
-        <v>70.11</v>
+        <v>83.68</v>
       </c>
       <c r="K43">
-        <v>77.86</v>
+        <v>78.239999999999995</v>
       </c>
       <c r="L43">
-        <v>88.04</v>
+        <v>78.790000000000006</v>
+      </c>
+      <c r="M43">
+        <v>86</v>
+      </c>
+      <c r="N43">
+        <v>71.47</v>
       </c>
       <c r="O43">
-        <v>92.06</v>
+        <v>87.72</v>
+      </c>
+      <c r="P43">
+        <v>91.47</v>
       </c>
       <c r="Q43">
-        <v>68</v>
+        <v>95.78</v>
+      </c>
+      <c r="R43">
+        <v>79.31</v>
       </c>
       <c r="S43">
-        <v>7.39</v>
+        <v>62.28</v>
       </c>
       <c r="T43">
-        <v>94.22</v>
+        <v>76.930000000000007</v>
+      </c>
+      <c r="U43">
+        <v>86.13</v>
+      </c>
+      <c r="V43">
+        <v>87.61</v>
+      </c>
+      <c r="W43">
+        <v>77.66</v>
       </c>
       <c r="X43">
-        <v>90.93</v>
+        <v>89.46</v>
       </c>
       <c r="Y43">
-        <v>96.3</v>
+        <v>81.540000000000006</v>
       </c>
       <c r="Z43">
+        <v>89.33</v>
+      </c>
+      <c r="AA43">
         <v>86</v>
       </c>
-      <c r="AA43">
-        <v>64.63</v>
+      <c r="AB43">
+        <v>117.85</v>
       </c>
     </row>
     <row r="44" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B44">
         <v>20250930</v>
@@ -14620,72 +14674,60 @@
         <v>1</v>
       </c>
       <c r="D44">
-        <v>75.03</v>
+        <v>78.489999999999995</v>
       </c>
       <c r="E44">
-        <v>91.68</v>
+        <v>75.709999999999994</v>
       </c>
       <c r="F44">
-        <v>68.77</v>
+        <v>106.04</v>
+      </c>
+      <c r="G44">
+        <v>99</v>
       </c>
       <c r="H44">
-        <v>77.31</v>
-      </c>
-      <c r="I44">
-        <v>92.15</v>
+        <v>98.35</v>
       </c>
       <c r="J44">
-        <v>46.59</v>
+        <v>63.91</v>
       </c>
       <c r="K44">
-        <v>55</v>
+        <v>73.02</v>
       </c>
       <c r="L44">
-        <v>78.06</v>
-      </c>
-      <c r="N44">
-        <v>61.02</v>
-      </c>
-      <c r="O44">
-        <v>90.02</v>
+        <v>82.79</v>
+      </c>
+      <c r="P44">
+        <v>94.36</v>
       </c>
       <c r="Q44">
-        <v>65.34</v>
-      </c>
-      <c r="R44">
-        <v>95.57</v>
+        <v>75.150000000000006</v>
       </c>
       <c r="S44">
-        <v>82.01</v>
+        <v>88.88</v>
       </c>
       <c r="T44">
-        <v>60.04</v>
+        <v>87.74</v>
       </c>
       <c r="U44">
-        <v>79.61</v>
+        <v>84.55</v>
       </c>
       <c r="V44">
-        <v>65.22</v>
+        <v>86.28</v>
       </c>
       <c r="W44">
-        <v>88.5</v>
-      </c>
-      <c r="X44">
-        <v>94.45</v>
+        <v>78.25</v>
       </c>
       <c r="Y44">
-        <v>67.489999999999995</v>
-      </c>
-      <c r="AA44">
-        <v>160</v>
-      </c>
-      <c r="AB44">
-        <v>108</v>
+        <v>114.46</v>
+      </c>
+      <c r="Z44">
+        <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B45">
         <v>20250930</v>
@@ -14694,731 +14736,650 @@
         <v>1</v>
       </c>
       <c r="D45">
-        <v>77.61</v>
+        <v>78.510000000000005</v>
       </c>
       <c r="E45">
-        <v>70.040000000000006</v>
+        <v>69.89</v>
       </c>
       <c r="F45">
-        <v>79.23</v>
+        <v>72.099999999999994</v>
+      </c>
+      <c r="G45">
+        <v>83.15</v>
       </c>
       <c r="H45">
-        <v>74.75</v>
+        <v>107.29</v>
       </c>
       <c r="I45">
-        <v>85.79</v>
+        <v>86.32</v>
+      </c>
+      <c r="J45">
+        <v>65.760000000000005</v>
+      </c>
+      <c r="K45">
+        <v>110</v>
       </c>
       <c r="L45">
-        <v>71.91</v>
+        <v>89</v>
+      </c>
+      <c r="N45">
+        <v>78.67</v>
       </c>
       <c r="O45">
-        <v>82.23</v>
-      </c>
-      <c r="S45">
-        <v>0</v>
+        <v>86</v>
+      </c>
+      <c r="Q45">
+        <v>89.01</v>
+      </c>
+      <c r="R45">
+        <v>85.13</v>
       </c>
       <c r="T45">
-        <v>99</v>
+        <v>86.26</v>
       </c>
       <c r="U45">
-        <v>73.84</v>
+        <v>76.19</v>
       </c>
       <c r="W45">
-        <v>66.98</v>
-      </c>
-      <c r="Y45">
-        <v>81.17</v>
+        <v>96.18</v>
+      </c>
+      <c r="AA45">
+        <v>86</v>
       </c>
       <c r="AB45">
-        <v>87.5</v>
+        <v>80.64</v>
       </c>
     </row>
     <row r="46" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B46">
         <v>20250930</v>
       </c>
       <c r="C46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46">
-        <v>7.99</v>
+        <v>75.64</v>
       </c>
       <c r="E46">
-        <v>8.4499999999999993</v>
+        <v>71.709999999999994</v>
       </c>
       <c r="F46">
-        <v>8.19</v>
+        <v>75.650000000000006</v>
       </c>
       <c r="G46">
-        <v>8.5</v>
+        <v>72.55</v>
       </c>
       <c r="H46">
-        <v>8.99</v>
+        <v>74.42</v>
       </c>
       <c r="I46">
-        <v>9</v>
+        <v>88.88</v>
       </c>
       <c r="J46">
-        <v>10.220000000000001</v>
+        <v>68.819999999999993</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>88.39</v>
       </c>
       <c r="L46">
-        <v>7.49</v>
+        <v>72.760000000000005</v>
       </c>
       <c r="M46">
-        <v>0</v>
+        <v>74.150000000000006</v>
       </c>
       <c r="N46">
-        <v>8.23</v>
+        <v>89</v>
       </c>
       <c r="O46">
-        <v>6.65</v>
+        <v>74.77</v>
       </c>
       <c r="P46">
-        <v>10.5</v>
+        <v>98.02</v>
       </c>
       <c r="Q46">
-        <v>6.52</v>
+        <v>80.900000000000006</v>
       </c>
       <c r="R46">
-        <v>10.14</v>
+        <v>84.63</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>83.27</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>89.73</v>
       </c>
       <c r="U46">
-        <v>8.73</v>
+        <v>75.989999999999995</v>
       </c>
       <c r="V46">
-        <v>7.6</v>
+        <v>72.89</v>
       </c>
       <c r="W46">
-        <v>7.4</v>
+        <v>65.55</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>85.46</v>
       </c>
       <c r="Y46">
-        <v>6.14</v>
+        <v>77.3</v>
       </c>
       <c r="Z46">
-        <v>8.8000000000000007</v>
+        <v>85.46</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AB46">
-        <v>7.85</v>
+        <v>71.45</v>
       </c>
     </row>
     <row r="47" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B47">
         <v>20250930</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47">
-        <v>7.29</v>
+        <v>78.37</v>
       </c>
       <c r="E47">
-        <v>6.93</v>
+        <v>44.61</v>
       </c>
       <c r="F47">
-        <v>7.25</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
+        <v>79.34</v>
       </c>
       <c r="H47">
-        <v>8.67</v>
+        <v>60.2</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>75.510000000000005</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>70.11</v>
       </c>
       <c r="K47">
-        <v>15</v>
+        <v>77.86</v>
       </c>
       <c r="L47">
-        <v>5.49</v>
-      </c>
-      <c r="M47">
-        <v>0</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
+        <v>88.04</v>
       </c>
       <c r="O47">
-        <v>0</v>
-      </c>
-      <c r="P47">
-        <v>0</v>
+        <v>92.06</v>
       </c>
       <c r="Q47">
-        <v>7.36</v>
-      </c>
-      <c r="R47">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="S47">
-        <v>8.56</v>
+        <v>7.39</v>
       </c>
       <c r="T47">
-        <v>8.69</v>
-      </c>
-      <c r="U47">
-        <v>0</v>
-      </c>
-      <c r="V47">
-        <v>0</v>
-      </c>
-      <c r="W47">
-        <v>0</v>
+        <v>94.22</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>90.93</v>
       </c>
       <c r="Y47">
-        <v>5.5</v>
+        <v>96.3</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AA47">
-        <v>0</v>
-      </c>
-      <c r="AB47">
-        <v>7.13</v>
+        <v>64.63</v>
       </c>
     </row>
     <row r="48" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B48">
         <v>20250930</v>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48">
-        <v>9.08</v>
+        <v>75.03</v>
       </c>
       <c r="E48">
-        <v>7.31</v>
+        <v>91.68</v>
       </c>
       <c r="F48">
-        <v>0</v>
-      </c>
-      <c r="G48">
-        <v>0</v>
+        <v>68.77</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>77.31</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>92.15</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>46.59</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
+        <v>78.06</v>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>61.02</v>
       </c>
       <c r="O48">
-        <v>0</v>
-      </c>
-      <c r="P48">
-        <v>6</v>
+        <v>90.02</v>
       </c>
       <c r="Q48">
-        <v>9.5399999999999991</v>
+        <v>65.34</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>95.57</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>82.01</v>
       </c>
       <c r="T48">
-        <v>6.5</v>
+        <v>60.04</v>
       </c>
       <c r="U48">
-        <v>9.4499999999999993</v>
+        <v>79.61</v>
       </c>
       <c r="V48">
-        <v>9.67</v>
+        <v>65.22</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>88.5</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>94.45</v>
       </c>
       <c r="Y48">
-        <v>0</v>
-      </c>
-      <c r="Z48">
-        <v>0</v>
+        <v>67.489999999999995</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AB48">
-        <v>7.86</v>
+        <v>108</v>
       </c>
     </row>
     <row r="49" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B49">
         <v>20250930</v>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>7.86</v>
+        <v>77.61</v>
       </c>
       <c r="E49">
-        <v>7.08</v>
+        <v>70.040000000000006</v>
       </c>
       <c r="F49">
-        <v>0</v>
-      </c>
-      <c r="G49">
-        <v>0</v>
+        <v>79.23</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>74.75</v>
       </c>
       <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
+        <v>85.79</v>
       </c>
       <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
-      <c r="N49">
-        <v>4.9400000000000004</v>
+        <v>71.91</v>
       </c>
       <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
-        <v>0</v>
-      </c>
-      <c r="Q49">
-        <v>0</v>
-      </c>
-      <c r="R49">
-        <v>0</v>
+        <v>82.23</v>
       </c>
       <c r="S49">
         <v>0</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="U49">
-        <v>9</v>
-      </c>
-      <c r="V49">
-        <v>0</v>
+        <v>73.84</v>
       </c>
       <c r="W49">
-        <v>0</v>
-      </c>
-      <c r="X49">
-        <v>0</v>
+        <v>66.98</v>
       </c>
       <c r="Y49">
-        <v>0</v>
-      </c>
-      <c r="Z49">
-        <v>0</v>
-      </c>
-      <c r="AA49">
-        <v>0</v>
+        <v>81.17</v>
       </c>
       <c r="AB49">
-        <v>7.25</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="50" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B50">
         <v>20250930</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>8.11</v>
+        <v>75.459999999999994</v>
       </c>
       <c r="E50">
-        <v>7.92</v>
+        <v>59.08</v>
       </c>
       <c r="F50">
-        <v>8.5500000000000007</v>
+        <v>77.680000000000007</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>102.22</v>
       </c>
       <c r="H50">
-        <v>9.44</v>
+        <v>77.900000000000006</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>87.71</v>
       </c>
       <c r="J50">
-        <v>15</v>
+        <v>45.13</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>86.93</v>
       </c>
       <c r="L50">
-        <v>8.42</v>
+        <v>82.51</v>
       </c>
       <c r="M50">
-        <v>1</v>
+        <v>59.2</v>
       </c>
       <c r="N50">
-        <v>9.25</v>
+        <v>89.94</v>
       </c>
       <c r="O50">
-        <v>12.18</v>
+        <v>119.31</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="Q50">
-        <v>9.01</v>
-      </c>
-      <c r="R50">
-        <v>0</v>
+        <v>77.39</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>106.51</v>
       </c>
       <c r="T50">
-        <v>15</v>
+        <v>91.16</v>
       </c>
       <c r="U50">
-        <v>8.73</v>
+        <v>89.37</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>81.05</v>
       </c>
       <c r="W50">
-        <v>9</v>
-      </c>
-      <c r="X50">
-        <v>0</v>
+        <v>95.44</v>
       </c>
       <c r="Y50">
-        <v>4.7</v>
+        <v>72.599999999999994</v>
       </c>
       <c r="Z50">
-        <v>10.5</v>
-      </c>
-      <c r="AA50">
-        <v>0</v>
+        <v>64.33</v>
       </c>
       <c r="AB50">
-        <v>7.04</v>
+        <v>154.72</v>
       </c>
     </row>
     <row r="51" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B51">
         <v>20250930</v>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>6.73</v>
+        <v>70.72</v>
       </c>
       <c r="E51">
-        <v>11</v>
+        <v>69.5</v>
       </c>
       <c r="F51">
-        <v>6.77</v>
+        <v>66.81</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>89.23</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>75.400000000000006</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>36.72</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>75.38</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>63.89</v>
       </c>
       <c r="L51">
-        <v>4</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="M51">
-        <v>0</v>
+        <v>91.55</v>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>68.430000000000007</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>68.17</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>67.680000000000007</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>65.3</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>67.63</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>77.17</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>70.150000000000006</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>75.430000000000007</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>74.89</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>80.849999999999994</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>79.86</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>72.86</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>52.1</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>71.930000000000007</v>
       </c>
     </row>
     <row r="52" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B52">
         <v>20250930</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52">
-        <v>9.3000000000000007</v>
+        <v>62.6</v>
       </c>
       <c r="E52">
-        <v>7.62</v>
+        <v>59.41</v>
       </c>
       <c r="F52">
-        <v>7.48</v>
-      </c>
-      <c r="G52">
-        <v>0</v>
+        <v>68.36</v>
       </c>
       <c r="H52">
-        <v>9.6199999999999992</v>
+        <v>62.71</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>97.52</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>143.85</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>62.86</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>49.65</v>
       </c>
       <c r="M52">
-        <v>0</v>
-      </c>
-      <c r="N52">
-        <v>0</v>
-      </c>
-      <c r="O52">
-        <v>0</v>
+        <v>69.569999999999993</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>70.400000000000006</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>87.13</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>75.36</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>59.84</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>79.61</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>77.400000000000006</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>81.22</v>
       </c>
       <c r="Y52">
-        <v>10.66</v>
-      </c>
-      <c r="Z52">
-        <v>0</v>
+        <v>64.02</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>39.5</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>82.61</v>
       </c>
     </row>
     <row r="53" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B53">
         <v>20250930</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53">
-        <v>8.74</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="E53">
-        <v>8.81</v>
+        <v>56.74</v>
       </c>
       <c r="F53">
-        <v>6.16</v>
+        <v>72.44</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>90.82</v>
       </c>
       <c r="H53">
-        <v>9.68</v>
+        <v>63.77</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>33.85</v>
       </c>
       <c r="J53">
-        <v>0</v>
+        <v>57.62</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>73.94</v>
       </c>
       <c r="L53">
-        <v>2.7</v>
+        <v>57.52</v>
       </c>
       <c r="M53">
-        <v>0</v>
+        <v>86.82</v>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>63.68</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>54.83</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>109.35</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>79.64</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>69.69</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>68.790000000000006</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>29.19</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>56.48</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>84.24</v>
       </c>
       <c r="W53">
-        <v>1</v>
+        <v>72.67</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>91.17</v>
       </c>
       <c r="Y53">
-        <v>9.1199999999999992</v>
+        <v>62.2</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>74.010000000000005</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>46.27</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>59.41</v>
       </c>
     </row>
     <row r="54" spans="1:28" x14ac:dyDescent="0.25">
@@ -15426,85 +15387,85 @@
         <v>3</v>
       </c>
       <c r="B54">
-        <v>20251231</v>
+        <v>20250930</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54">
-        <v>51.65</v>
+        <v>7.99</v>
       </c>
       <c r="E54">
-        <v>53.73</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="F54">
-        <v>55.34</v>
+        <v>8.19</v>
       </c>
       <c r="G54">
-        <v>58.31</v>
+        <v>8.5</v>
       </c>
       <c r="H54">
-        <v>47.74</v>
+        <v>8.99</v>
       </c>
       <c r="I54">
-        <v>45.35</v>
+        <v>9</v>
       </c>
       <c r="J54">
-        <v>45.62</v>
+        <v>10.220000000000001</v>
       </c>
       <c r="K54">
-        <v>42.58</v>
+        <v>0</v>
       </c>
       <c r="L54">
-        <v>50.95</v>
+        <v>7.49</v>
       </c>
       <c r="M54">
-        <v>63.6</v>
+        <v>0</v>
       </c>
       <c r="N54">
-        <v>54.66</v>
+        <v>8.23</v>
       </c>
       <c r="O54">
-        <v>59.49</v>
+        <v>6.65</v>
       </c>
       <c r="P54">
-        <v>48.79</v>
+        <v>10.5</v>
       </c>
       <c r="Q54">
-        <v>51.91</v>
+        <v>6.52</v>
       </c>
       <c r="R54">
-        <v>41.09</v>
+        <v>10.14</v>
       </c>
       <c r="S54">
-        <v>44.32</v>
+        <v>0</v>
       </c>
       <c r="T54">
-        <v>57.19</v>
+        <v>0</v>
       </c>
       <c r="U54">
-        <v>49.07</v>
+        <v>8.73</v>
       </c>
       <c r="V54">
-        <v>40.479999999999997</v>
+        <v>7.6</v>
       </c>
       <c r="W54">
-        <v>47.69</v>
+        <v>7.4</v>
       </c>
       <c r="X54">
-        <v>87.33</v>
+        <v>0</v>
       </c>
       <c r="Y54">
-        <v>47.77</v>
+        <v>6.14</v>
       </c>
       <c r="Z54">
-        <v>53.88</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="AA54">
-        <v>36.17</v>
+        <v>0</v>
       </c>
       <c r="AB54">
-        <v>53.69</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="55" spans="1:28" x14ac:dyDescent="0.25">
@@ -15512,79 +15473,85 @@
         <v>4</v>
       </c>
       <c r="B55">
-        <v>20251231</v>
+        <v>20250930</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55">
-        <v>53.5</v>
+        <v>7.29</v>
       </c>
       <c r="E55">
-        <v>55.91</v>
+        <v>6.93</v>
       </c>
       <c r="F55">
-        <v>54.54</v>
+        <v>7.25</v>
       </c>
       <c r="G55">
-        <v>59.14</v>
+        <v>0</v>
       </c>
       <c r="H55">
-        <v>54.66</v>
+        <v>8.67</v>
       </c>
       <c r="I55">
-        <v>57.71</v>
+        <v>0</v>
       </c>
       <c r="J55">
-        <v>65.05</v>
+        <v>0</v>
       </c>
       <c r="K55">
-        <v>49.51</v>
+        <v>15</v>
       </c>
       <c r="L55">
-        <v>50.39</v>
+        <v>5.49</v>
       </c>
       <c r="M55">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="N55">
-        <v>42.44</v>
+        <v>0</v>
       </c>
       <c r="O55">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="P55">
-        <v>54.82</v>
+        <v>0</v>
       </c>
       <c r="Q55">
-        <v>58.04</v>
+        <v>7.36</v>
       </c>
       <c r="R55">
-        <v>34.92</v>
+        <v>0</v>
       </c>
       <c r="S55">
-        <v>64.739999999999995</v>
+        <v>8.56</v>
       </c>
       <c r="T55">
-        <v>42.97</v>
+        <v>8.69</v>
       </c>
       <c r="U55">
-        <v>50.79</v>
+        <v>0</v>
       </c>
       <c r="V55">
-        <v>64.8</v>
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0</v>
       </c>
       <c r="X55">
-        <v>101.5</v>
+        <v>0</v>
       </c>
       <c r="Y55">
-        <v>53.06</v>
+        <v>5.5</v>
       </c>
       <c r="Z55">
-        <v>60.66</v>
+        <v>0</v>
+      </c>
+      <c r="AA55">
+        <v>0</v>
       </c>
       <c r="AB55">
-        <v>49.67</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="56" spans="1:28" x14ac:dyDescent="0.25">
@@ -15592,67 +15559,85 @@
         <v>5</v>
       </c>
       <c r="B56">
-        <v>20251231</v>
+        <v>20250930</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56">
-        <v>48.88</v>
+        <v>9.08</v>
       </c>
       <c r="E56">
-        <v>53.1</v>
+        <v>7.31</v>
       </c>
       <c r="F56">
-        <v>92.4</v>
+        <v>0</v>
       </c>
       <c r="G56">
-        <v>85.4</v>
+        <v>0</v>
       </c>
       <c r="H56">
-        <v>47.79</v>
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
       </c>
       <c r="J56">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K56">
-        <v>42.01</v>
+        <v>0</v>
       </c>
       <c r="L56">
-        <v>95.1</v>
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
       </c>
       <c r="N56">
-        <v>34.99</v>
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
       </c>
       <c r="P56">
-        <v>51.73</v>
+        <v>6</v>
       </c>
       <c r="Q56">
-        <v>47.99</v>
+        <v>9.5399999999999991</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
       </c>
       <c r="S56">
-        <v>38.92</v>
+        <v>0</v>
       </c>
       <c r="T56">
-        <v>62.38</v>
+        <v>6.5</v>
       </c>
       <c r="U56">
-        <v>41.02</v>
+        <v>9.4499999999999993</v>
       </c>
       <c r="V56">
-        <v>51.79</v>
+        <v>9.67</v>
       </c>
       <c r="W56">
-        <v>53.67</v>
+        <v>0</v>
+      </c>
+      <c r="X56">
+        <v>0</v>
       </c>
       <c r="Y56">
-        <v>77.06</v>
+        <v>0</v>
       </c>
       <c r="Z56">
-        <v>91</v>
+        <v>0</v>
+      </c>
+      <c r="AA56">
+        <v>0</v>
       </c>
       <c r="AB56">
-        <v>45.02</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="57" spans="1:28" x14ac:dyDescent="0.25">
@@ -15660,58 +15645,85 @@
         <v>6</v>
       </c>
       <c r="B57">
-        <v>20251231</v>
+        <v>20250930</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57">
-        <v>44.68</v>
+        <v>7.86</v>
       </c>
       <c r="E57">
-        <v>34.31</v>
+        <v>7.08</v>
       </c>
       <c r="F57">
-        <v>77.760000000000005</v>
+        <v>0</v>
       </c>
       <c r="G57">
-        <v>48.18</v>
+        <v>0</v>
       </c>
       <c r="H57">
-        <v>108.61</v>
+        <v>0</v>
       </c>
       <c r="I57">
-        <v>87.96</v>
+        <v>0</v>
       </c>
       <c r="J57">
-        <v>54.51</v>
+        <v>0</v>
       </c>
       <c r="K57">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="L57">
-        <v>45.84</v>
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
       </c>
       <c r="N57">
-        <v>46.45</v>
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
       </c>
       <c r="Q57">
-        <v>105.94</v>
+        <v>0</v>
       </c>
       <c r="R57">
-        <v>44.15</v>
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>0</v>
       </c>
       <c r="U57">
-        <v>43.15</v>
+        <v>9</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
       </c>
       <c r="W57">
-        <v>56.1</v>
+        <v>0</v>
+      </c>
+      <c r="X57">
+        <v>0</v>
       </c>
       <c r="Y57">
-        <v>45.82</v>
+        <v>0</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+      <c r="AA57">
+        <v>0</v>
       </c>
       <c r="AB57">
-        <v>54.15</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="58" spans="1:28" x14ac:dyDescent="0.25">
@@ -15719,85 +15731,85 @@
         <v>7</v>
       </c>
       <c r="B58">
-        <v>20251231</v>
+        <v>20250930</v>
       </c>
       <c r="C58">
+        <v>2</v>
+      </c>
+      <c r="D58">
+        <v>8.11</v>
+      </c>
+      <c r="E58">
+        <v>7.92</v>
+      </c>
+      <c r="F58">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>9.44</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>15</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>8.42</v>
+      </c>
+      <c r="M58">
         <v>1</v>
       </c>
-      <c r="D58">
-        <v>56.49</v>
-      </c>
-      <c r="E58">
-        <v>57.14</v>
-      </c>
-      <c r="F58">
-        <v>55.71</v>
-      </c>
-      <c r="G58">
-        <v>54.55</v>
-      </c>
-      <c r="H58">
-        <v>49.76</v>
-      </c>
-      <c r="I58">
-        <v>66.87</v>
-      </c>
-      <c r="J58">
-        <v>48.66</v>
-      </c>
-      <c r="K58">
-        <v>45.45</v>
-      </c>
-      <c r="L58">
-        <v>56.17</v>
-      </c>
-      <c r="M58">
-        <v>49.48</v>
-      </c>
       <c r="N58">
-        <v>50.9</v>
+        <v>9.25</v>
       </c>
       <c r="O58">
-        <v>66.14</v>
+        <v>12.18</v>
       </c>
       <c r="P58">
-        <v>80.849999999999994</v>
+        <v>0</v>
       </c>
       <c r="Q58">
-        <v>54.27</v>
+        <v>9.01</v>
       </c>
       <c r="R58">
-        <v>34.880000000000003</v>
+        <v>0</v>
       </c>
       <c r="S58">
-        <v>63.08</v>
+        <v>0</v>
       </c>
       <c r="T58">
-        <v>65.06</v>
+        <v>15</v>
       </c>
       <c r="U58">
-        <v>55.3</v>
+        <v>8.73</v>
       </c>
       <c r="V58">
-        <v>67.849999999999994</v>
+        <v>0</v>
       </c>
       <c r="W58">
-        <v>61.54</v>
+        <v>9</v>
       </c>
       <c r="X58">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="Y58">
-        <v>51.91</v>
+        <v>4.7</v>
       </c>
       <c r="Z58">
-        <v>55.07</v>
+        <v>10.5</v>
       </c>
       <c r="AA58">
-        <v>44.15</v>
+        <v>0</v>
       </c>
       <c r="AB58">
-        <v>54.39</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="59" spans="1:28" x14ac:dyDescent="0.25">
@@ -15805,64 +15817,85 @@
         <v>8</v>
       </c>
       <c r="B59">
-        <v>20251231</v>
+        <v>20250930</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59">
-        <v>53.27</v>
+        <v>6.73</v>
       </c>
       <c r="E59">
-        <v>62.87</v>
+        <v>11</v>
       </c>
       <c r="F59">
-        <v>46.33</v>
+        <v>6.77</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
       </c>
       <c r="H59">
-        <v>67.56</v>
+        <v>0</v>
       </c>
       <c r="I59">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="J59">
-        <v>82.22</v>
+        <v>0</v>
       </c>
       <c r="K59">
-        <v>50.62</v>
+        <v>0</v>
       </c>
       <c r="L59">
-        <v>96.8</v>
+        <v>4</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
       </c>
       <c r="N59">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="O59">
-        <v>48</v>
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
       </c>
       <c r="Q59">
-        <v>37.28</v>
+        <v>0</v>
       </c>
       <c r="R59">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="S59">
-        <v>65.06</v>
+        <v>0</v>
       </c>
       <c r="T59">
-        <v>59.64</v>
+        <v>0</v>
       </c>
       <c r="U59">
-        <v>32</v>
+        <v>0</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0</v>
       </c>
       <c r="X59">
-        <v>59.81</v>
+        <v>0</v>
       </c>
       <c r="Y59">
-        <v>64.16</v>
+        <v>0</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
       </c>
       <c r="AA59">
-        <v>59.08</v>
+        <v>0</v>
+      </c>
+      <c r="AB59">
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:28" x14ac:dyDescent="0.25">
@@ -15870,64 +15903,85 @@
         <v>9</v>
       </c>
       <c r="B60">
-        <v>20251231</v>
+        <v>20250930</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60">
-        <v>49.75</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="E60">
-        <v>52.77</v>
+        <v>7.62</v>
       </c>
       <c r="F60">
-        <v>51.09</v>
+        <v>7.48</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
       </c>
       <c r="H60">
-        <v>49.04</v>
+        <v>9.6199999999999992</v>
       </c>
       <c r="I60">
-        <v>60.37</v>
+        <v>0</v>
       </c>
       <c r="J60">
-        <v>33.65</v>
+        <v>0</v>
       </c>
       <c r="K60">
-        <v>52.9</v>
+        <v>0</v>
       </c>
       <c r="L60">
-        <v>73.819999999999993</v>
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
       </c>
       <c r="N60">
-        <v>39.26</v>
+        <v>0</v>
       </c>
       <c r="O60">
-        <v>54.7</v>
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
       </c>
       <c r="Q60">
-        <v>92.86</v>
+        <v>0</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
       </c>
       <c r="S60">
-        <v>53.85</v>
+        <v>0</v>
       </c>
       <c r="T60">
-        <v>70.45</v>
+        <v>0</v>
       </c>
       <c r="U60">
-        <v>38.89</v>
+        <v>0</v>
       </c>
       <c r="V60">
-        <v>34.39</v>
+        <v>0</v>
       </c>
       <c r="W60">
-        <v>85.74</v>
+        <v>0</v>
+      </c>
+      <c r="X60">
+        <v>0</v>
       </c>
       <c r="Y60">
-        <v>43.91</v>
+        <v>10.66</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+      <c r="AA60">
+        <v>0</v>
       </c>
       <c r="AB60">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:28" x14ac:dyDescent="0.25">
@@ -15935,49 +15989,85 @@
         <v>10</v>
       </c>
       <c r="B61">
-        <v>20251231</v>
+        <v>20250930</v>
       </c>
       <c r="C61">
+        <v>2</v>
+      </c>
+      <c r="D61">
+        <v>8.74</v>
+      </c>
+      <c r="E61">
+        <v>8.81</v>
+      </c>
+      <c r="F61">
+        <v>6.16</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>9.68</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>2.7</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>0</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>0</v>
+      </c>
+      <c r="T61">
+        <v>0</v>
+      </c>
+      <c r="U61">
+        <v>0</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61">
         <v>1</v>
       </c>
-      <c r="D61">
-        <v>51.05</v>
-      </c>
-      <c r="E61">
-        <v>46.09</v>
-      </c>
-      <c r="F61">
-        <v>59.68</v>
-      </c>
-      <c r="H61">
-        <v>48.55</v>
-      </c>
-      <c r="I61">
-        <v>87.08</v>
-      </c>
-      <c r="L61">
-        <v>44.98</v>
-      </c>
-      <c r="O61">
-        <v>59.93</v>
-      </c>
-      <c r="S61">
-        <v>0</v>
-      </c>
-      <c r="T61">
-        <v>70</v>
-      </c>
-      <c r="U61">
-        <v>43.19</v>
-      </c>
-      <c r="W61">
-        <v>72.17</v>
+      <c r="X61">
+        <v>0</v>
       </c>
       <c r="Y61">
-        <v>52.31</v>
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+      <c r="AA61">
+        <v>0</v>
       </c>
       <c r="AB61">
-        <v>49.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:28" x14ac:dyDescent="0.25">
@@ -15988,82 +16078,82 @@
         <v>20251231</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62">
-        <v>7.63</v>
+        <v>51.65</v>
       </c>
       <c r="E62">
-        <v>7.59</v>
+        <v>53.73</v>
       </c>
       <c r="F62">
-        <v>7.77</v>
+        <v>55.34</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>58.31</v>
       </c>
       <c r="H62">
-        <v>7.94</v>
+        <v>47.74</v>
       </c>
       <c r="I62">
-        <v>5.5</v>
+        <v>45.35</v>
       </c>
       <c r="J62">
-        <v>9.7200000000000006</v>
+        <v>45.62</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>42.58</v>
       </c>
       <c r="L62">
-        <v>7.89</v>
+        <v>50.95</v>
       </c>
       <c r="M62">
-        <v>0</v>
+        <v>63.6</v>
       </c>
       <c r="N62">
-        <v>6.42</v>
+        <v>54.66</v>
       </c>
       <c r="O62">
-        <v>7.43</v>
+        <v>59.49</v>
       </c>
       <c r="P62">
-        <v>8.77</v>
+        <v>48.79</v>
       </c>
       <c r="Q62">
-        <v>5.03</v>
+        <v>51.91</v>
       </c>
       <c r="R62">
-        <v>4.97</v>
+        <v>41.09</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>44.32</v>
       </c>
       <c r="T62">
-        <v>8</v>
+        <v>57.19</v>
       </c>
       <c r="U62">
-        <v>5.66</v>
+        <v>49.07</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>40.479999999999997</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>47.69</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>87.33</v>
       </c>
       <c r="Y62">
-        <v>7.1</v>
+        <v>47.77</v>
       </c>
       <c r="Z62">
-        <v>7.74</v>
+        <v>53.88</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>36.17</v>
       </c>
       <c r="AB62">
-        <v>7.72</v>
+        <v>53.69</v>
       </c>
     </row>
     <row r="63" spans="1:28" x14ac:dyDescent="0.25">
@@ -16074,82 +16164,76 @@
         <v>20251231</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63">
-        <v>6.12</v>
+        <v>53.5</v>
       </c>
       <c r="E63">
-        <v>7.39</v>
+        <v>55.91</v>
       </c>
       <c r="F63">
-        <v>8.81</v>
+        <v>54.54</v>
       </c>
       <c r="G63">
-        <v>8.5</v>
+        <v>59.14</v>
       </c>
       <c r="H63">
-        <v>7.37</v>
+        <v>54.66</v>
       </c>
       <c r="I63">
-        <v>0</v>
+        <v>57.71</v>
       </c>
       <c r="J63">
-        <v>0</v>
+        <v>65.05</v>
       </c>
       <c r="K63">
-        <v>0</v>
+        <v>49.51</v>
       </c>
       <c r="L63">
-        <v>2.19</v>
+        <v>50.39</v>
       </c>
       <c r="M63">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="N63">
-        <v>9.25</v>
+        <v>42.44</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>54.82</v>
       </c>
       <c r="Q63">
-        <v>7.07</v>
+        <v>58.04</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>34.92</v>
       </c>
       <c r="S63">
-        <v>8.3000000000000007</v>
+        <v>64.739999999999995</v>
       </c>
       <c r="T63">
-        <v>6.2</v>
+        <v>42.97</v>
       </c>
       <c r="U63">
-        <v>8.33</v>
+        <v>50.79</v>
       </c>
       <c r="V63">
-        <v>0</v>
-      </c>
-      <c r="W63">
-        <v>0</v>
+        <v>64.8</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>101.5</v>
       </c>
       <c r="Y63">
-        <v>8.17</v>
+        <v>53.06</v>
       </c>
       <c r="Z63">
-        <v>0</v>
-      </c>
-      <c r="AA63">
-        <v>0</v>
+        <v>60.66</v>
       </c>
       <c r="AB63">
-        <v>5.07</v>
+        <v>49.67</v>
       </c>
     </row>
     <row r="64" spans="1:28" x14ac:dyDescent="0.25">
@@ -16160,82 +16244,64 @@
         <v>20251231</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64">
-        <v>7.32</v>
+        <v>48.88</v>
       </c>
       <c r="E64">
-        <v>7.49</v>
+        <v>53.1</v>
       </c>
       <c r="F64">
-        <v>10</v>
+        <v>92.4</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>85.4</v>
       </c>
       <c r="H64">
-        <v>9</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
+        <v>47.79</v>
       </c>
       <c r="J64">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>42.01</v>
       </c>
       <c r="L64">
-        <v>0</v>
-      </c>
-      <c r="M64">
-        <v>0</v>
+        <v>95.1</v>
       </c>
       <c r="N64">
-        <v>0</v>
-      </c>
-      <c r="O64">
-        <v>0</v>
+        <v>34.99</v>
       </c>
       <c r="P64">
-        <v>8</v>
+        <v>51.73</v>
       </c>
       <c r="Q64">
-        <v>7.18</v>
-      </c>
-      <c r="R64">
-        <v>0</v>
+        <v>47.99</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>38.92</v>
       </c>
       <c r="T64">
-        <v>6.14</v>
+        <v>62.38</v>
       </c>
       <c r="U64">
-        <v>6.4</v>
+        <v>41.02</v>
       </c>
       <c r="V64">
-        <v>10.199999999999999</v>
+        <v>51.79</v>
       </c>
       <c r="W64">
-        <v>0</v>
-      </c>
-      <c r="X64">
-        <v>0</v>
+        <v>53.67</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>77.06</v>
       </c>
       <c r="Z64">
-        <v>0</v>
-      </c>
-      <c r="AA64">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>45.02</v>
       </c>
     </row>
     <row r="65" spans="1:28" x14ac:dyDescent="0.25">
@@ -16246,82 +16312,55 @@
         <v>20251231</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65">
-        <v>6.6</v>
+        <v>44.68</v>
       </c>
       <c r="E65">
-        <v>7.5</v>
+        <v>34.31</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>77.760000000000005</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>48.18</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>108.61</v>
       </c>
       <c r="I65">
-        <v>0</v>
+        <v>87.96</v>
       </c>
       <c r="J65">
-        <v>0</v>
+        <v>54.51</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65">
-        <v>0</v>
+        <v>45.84</v>
       </c>
       <c r="N65">
-        <v>9.4499999999999993</v>
-      </c>
-      <c r="O65">
-        <v>0</v>
-      </c>
-      <c r="P65">
-        <v>0</v>
+        <v>46.45</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>105.94</v>
       </c>
       <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="S65">
-        <v>0</v>
-      </c>
-      <c r="T65">
-        <v>0</v>
+        <v>44.15</v>
       </c>
       <c r="U65">
-        <v>6</v>
-      </c>
-      <c r="V65">
-        <v>0</v>
+        <v>43.15</v>
       </c>
       <c r="W65">
-        <v>0</v>
-      </c>
-      <c r="X65">
-        <v>0</v>
+        <v>56.1</v>
       </c>
       <c r="Y65">
-        <v>0</v>
-      </c>
-      <c r="Z65">
-        <v>0</v>
-      </c>
-      <c r="AA65">
-        <v>0</v>
+        <v>45.82</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>54.15</v>
       </c>
     </row>
     <row r="66" spans="1:28" x14ac:dyDescent="0.25">
@@ -16332,82 +16371,82 @@
         <v>20251231</v>
       </c>
       <c r="C66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66">
-        <v>7.95</v>
+        <v>56.49</v>
       </c>
       <c r="E66">
-        <v>8.27</v>
+        <v>57.14</v>
       </c>
       <c r="F66">
-        <v>7.41</v>
+        <v>55.71</v>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>54.55</v>
       </c>
       <c r="H66">
-        <v>8.85</v>
+        <v>49.76</v>
       </c>
       <c r="I66">
-        <v>6.5</v>
+        <v>66.87</v>
       </c>
       <c r="J66">
-        <v>4</v>
+        <v>48.66</v>
       </c>
       <c r="K66">
-        <v>0</v>
+        <v>45.45</v>
       </c>
       <c r="L66">
-        <v>8.8000000000000007</v>
+        <v>56.17</v>
       </c>
       <c r="M66">
-        <v>0</v>
+        <v>49.48</v>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>50.9</v>
       </c>
       <c r="O66">
-        <v>2.77</v>
+        <v>66.14</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>80.849999999999994</v>
       </c>
       <c r="Q66">
-        <v>4</v>
+        <v>54.27</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>34.880000000000003</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>63.08</v>
       </c>
       <c r="T66">
-        <v>4</v>
+        <v>65.06</v>
       </c>
       <c r="U66">
-        <v>8.01</v>
+        <v>55.3</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>67.849999999999994</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>61.54</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="Y66">
-        <v>8.1</v>
+        <v>51.91</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>55.07</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>44.15</v>
       </c>
       <c r="AB66">
-        <v>7.58</v>
+        <v>54.39</v>
       </c>
     </row>
     <row r="67" spans="1:28" x14ac:dyDescent="0.25">
@@ -16418,82 +16457,61 @@
         <v>20251231</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67">
-        <v>5.5</v>
+        <v>53.27</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>62.87</v>
       </c>
       <c r="F67">
-        <v>5.5</v>
-      </c>
-      <c r="G67">
-        <v>0</v>
+        <v>46.33</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>67.56</v>
       </c>
       <c r="I67">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="J67">
-        <v>0</v>
+        <v>82.22</v>
       </c>
       <c r="K67">
-        <v>0</v>
+        <v>50.62</v>
       </c>
       <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="O67">
-        <v>0</v>
-      </c>
-      <c r="P67">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>37.28</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>65.06</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>59.64</v>
       </c>
       <c r="U67">
-        <v>0</v>
-      </c>
-      <c r="V67">
-        <v>0</v>
-      </c>
-      <c r="W67">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>59.81</v>
       </c>
       <c r="Y67">
-        <v>0</v>
-      </c>
-      <c r="Z67">
-        <v>0</v>
+        <v>64.16</v>
       </c>
       <c r="AA67">
-        <v>0</v>
-      </c>
-      <c r="AB67">
-        <v>0</v>
+        <v>59.08</v>
       </c>
     </row>
     <row r="68" spans="1:28" x14ac:dyDescent="0.25">
@@ -16504,82 +16522,61 @@
         <v>20251231</v>
       </c>
       <c r="C68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D68">
-        <v>8.91</v>
+        <v>49.75</v>
       </c>
       <c r="E68">
-        <v>8.32</v>
+        <v>52.77</v>
       </c>
       <c r="F68">
-        <v>4.09</v>
-      </c>
-      <c r="G68">
-        <v>0</v>
+        <v>51.09</v>
       </c>
       <c r="H68">
-        <v>9.1</v>
+        <v>49.04</v>
       </c>
       <c r="I68">
-        <v>0</v>
+        <v>60.37</v>
       </c>
       <c r="J68">
-        <v>0</v>
+        <v>33.65</v>
       </c>
       <c r="K68">
-        <v>0</v>
+        <v>52.9</v>
       </c>
       <c r="L68">
-        <v>0</v>
-      </c>
-      <c r="M68">
-        <v>0</v>
+        <v>73.819999999999993</v>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>39.26</v>
       </c>
       <c r="O68">
-        <v>0</v>
-      </c>
-      <c r="P68">
-        <v>0</v>
+        <v>54.7</v>
       </c>
       <c r="Q68">
-        <v>0</v>
-      </c>
-      <c r="R68">
-        <v>0</v>
+        <v>92.86</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>53.85</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>70.45</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>38.89</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>34.39</v>
       </c>
       <c r="W68">
-        <v>0</v>
-      </c>
-      <c r="X68">
-        <v>0</v>
+        <v>85.74</v>
       </c>
       <c r="Y68">
-        <v>9.07</v>
-      </c>
-      <c r="Z68">
-        <v>0</v>
-      </c>
-      <c r="AA68">
-        <v>0</v>
+        <v>43.91</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69" spans="1:28" x14ac:dyDescent="0.25">
@@ -16590,81 +16587,1056 @@
         <v>20251231</v>
       </c>
       <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69">
+        <v>51.05</v>
+      </c>
+      <c r="E69">
+        <v>46.09</v>
+      </c>
+      <c r="F69">
+        <v>59.68</v>
+      </c>
+      <c r="H69">
+        <v>48.55</v>
+      </c>
+      <c r="I69">
+        <v>87.08</v>
+      </c>
+      <c r="L69">
+        <v>44.98</v>
+      </c>
+      <c r="O69">
+        <v>59.93</v>
+      </c>
+      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="T69">
+        <v>70</v>
+      </c>
+      <c r="U69">
+        <v>43.19</v>
+      </c>
+      <c r="W69">
+        <v>72.17</v>
+      </c>
+      <c r="Y69">
+        <v>52.31</v>
+      </c>
+      <c r="AB69">
+        <v>49.01</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70">
+        <v>20251231</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70">
+        <v>52.17</v>
+      </c>
+      <c r="E70">
+        <v>45.89</v>
+      </c>
+      <c r="F70">
+        <v>60.48</v>
+      </c>
+      <c r="G70">
+        <v>73.790000000000006</v>
+      </c>
+      <c r="H70">
+        <v>40.64</v>
+      </c>
+      <c r="I70">
+        <v>41.67</v>
+      </c>
+      <c r="J70">
+        <v>56.03</v>
+      </c>
+      <c r="K70">
+        <v>41.23</v>
+      </c>
+      <c r="L70">
+        <v>47.08</v>
+      </c>
+      <c r="M70">
+        <v>97.61</v>
+      </c>
+      <c r="N70">
+        <v>46.03</v>
+      </c>
+      <c r="O70">
+        <v>74.209999999999994</v>
+      </c>
+      <c r="Q70">
+        <v>73.290000000000006</v>
+      </c>
+      <c r="R70">
+        <v>70</v>
+      </c>
+      <c r="S70">
+        <v>122.23</v>
+      </c>
+      <c r="T70">
+        <v>71.36</v>
+      </c>
+      <c r="U70">
+        <v>50.8</v>
+      </c>
+      <c r="V70">
+        <v>65.63</v>
+      </c>
+      <c r="W70">
+        <v>64.89</v>
+      </c>
+      <c r="Y70">
+        <v>46.64</v>
+      </c>
+      <c r="Z70">
+        <v>38.39</v>
+      </c>
+      <c r="AB70">
+        <v>85.44</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>12</v>
+      </c>
+      <c r="B71">
+        <v>20251231</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71">
+        <v>50.72</v>
+      </c>
+      <c r="E71">
+        <v>55.2</v>
+      </c>
+      <c r="F71">
+        <v>49.6</v>
+      </c>
+      <c r="G71">
+        <v>59.78</v>
+      </c>
+      <c r="H71">
+        <v>52.86</v>
+      </c>
+      <c r="I71">
+        <v>36.71</v>
+      </c>
+      <c r="J71">
+        <v>55.6</v>
+      </c>
+      <c r="K71">
+        <v>39.67</v>
+      </c>
+      <c r="L71">
+        <v>36.72</v>
+      </c>
+      <c r="M71">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="N71">
+        <v>40.51</v>
+      </c>
+      <c r="O71">
+        <v>83.74</v>
+      </c>
+      <c r="P71">
+        <v>38.15</v>
+      </c>
+      <c r="Q71">
+        <v>45.5</v>
+      </c>
+      <c r="R71">
+        <v>52.6</v>
+      </c>
+      <c r="S71">
+        <v>33.229999999999997</v>
+      </c>
+      <c r="T71">
+        <v>43.14</v>
+      </c>
+      <c r="U71">
+        <v>44.38</v>
+      </c>
+      <c r="V71">
+        <v>48.69</v>
+      </c>
+      <c r="W71">
+        <v>51.57</v>
+      </c>
+      <c r="X71">
+        <v>58.24</v>
+      </c>
+      <c r="Y71">
+        <v>52.82</v>
+      </c>
+      <c r="Z71">
+        <v>53.34</v>
+      </c>
+      <c r="AA71">
+        <v>56.14</v>
+      </c>
+      <c r="AB71">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>13</v>
+      </c>
+      <c r="B72">
+        <v>20251231</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72">
+        <v>39.22</v>
+      </c>
+      <c r="E72">
+        <v>49.76</v>
+      </c>
+      <c r="F72">
+        <v>42.99</v>
+      </c>
+      <c r="H72">
+        <v>34.25</v>
+      </c>
+      <c r="I72">
+        <v>86.34</v>
+      </c>
+      <c r="J72">
+        <v>38.11</v>
+      </c>
+      <c r="K72">
+        <v>41.81</v>
+      </c>
+      <c r="L72">
+        <v>52.95</v>
+      </c>
+      <c r="M72">
+        <v>68.5</v>
+      </c>
+      <c r="Q72">
+        <v>69.209999999999994</v>
+      </c>
+      <c r="R72">
+        <v>34</v>
+      </c>
+      <c r="S72">
+        <v>81.63</v>
+      </c>
+      <c r="T72">
+        <v>48.01</v>
+      </c>
+      <c r="U72">
+        <v>39.11</v>
+      </c>
+      <c r="V72">
+        <v>105.83</v>
+      </c>
+      <c r="W72">
+        <v>35.75</v>
+      </c>
+      <c r="X72">
+        <v>49</v>
+      </c>
+      <c r="Y72">
+        <v>38.130000000000003</v>
+      </c>
+      <c r="Z72">
+        <v>159.81</v>
+      </c>
+      <c r="AA72">
+        <v>39.5</v>
+      </c>
+      <c r="AB72">
+        <v>32.93</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>14</v>
+      </c>
+      <c r="B73">
+        <v>20251231</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73">
+        <v>48.62</v>
+      </c>
+      <c r="E73">
+        <v>40.89</v>
+      </c>
+      <c r="F73">
+        <v>48.03</v>
+      </c>
+      <c r="G73">
+        <v>57.36</v>
+      </c>
+      <c r="H73">
+        <v>35.49</v>
+      </c>
+      <c r="I73">
+        <v>46.82</v>
+      </c>
+      <c r="J73">
+        <v>43.09</v>
+      </c>
+      <c r="K73">
+        <v>52.72</v>
+      </c>
+      <c r="L73">
+        <v>45.99</v>
+      </c>
+      <c r="M73">
+        <v>54.51</v>
+      </c>
+      <c r="N73">
+        <v>35.450000000000003</v>
+      </c>
+      <c r="O73">
+        <v>60.45</v>
+      </c>
+      <c r="P73">
+        <v>44.18</v>
+      </c>
+      <c r="Q73">
+        <v>43.78</v>
+      </c>
+      <c r="R73">
+        <v>29.21</v>
+      </c>
+      <c r="S73">
+        <v>62.37</v>
+      </c>
+      <c r="T73">
+        <v>52.85</v>
+      </c>
+      <c r="U73">
+        <v>35.35</v>
+      </c>
+      <c r="V73">
+        <v>100.23</v>
+      </c>
+      <c r="W73">
+        <v>43.8</v>
+      </c>
+      <c r="X73">
+        <v>52.23</v>
+      </c>
+      <c r="Y73">
+        <v>36.32</v>
+      </c>
+      <c r="Z73">
+        <v>54.11</v>
+      </c>
+      <c r="AA73">
+        <v>34.130000000000003</v>
+      </c>
+      <c r="AB73">
+        <v>30.37</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74">
+        <v>20251231</v>
+      </c>
+      <c r="C74">
         <v>2</v>
       </c>
-      <c r="D69">
+      <c r="D74">
+        <v>7.63</v>
+      </c>
+      <c r="E74">
+        <v>7.59</v>
+      </c>
+      <c r="F74">
+        <v>7.77</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>7.94</v>
+      </c>
+      <c r="I74">
+        <v>5.5</v>
+      </c>
+      <c r="J74">
+        <v>9.7200000000000006</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>7.89</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>6.42</v>
+      </c>
+      <c r="O74">
+        <v>7.43</v>
+      </c>
+      <c r="P74">
+        <v>8.77</v>
+      </c>
+      <c r="Q74">
+        <v>5.03</v>
+      </c>
+      <c r="R74">
+        <v>4.97</v>
+      </c>
+      <c r="S74">
+        <v>0</v>
+      </c>
+      <c r="T74">
+        <v>8</v>
+      </c>
+      <c r="U74">
+        <v>5.66</v>
+      </c>
+      <c r="V74">
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <v>0</v>
+      </c>
+      <c r="X74">
+        <v>0</v>
+      </c>
+      <c r="Y74">
+        <v>7.1</v>
+      </c>
+      <c r="Z74">
+        <v>7.74</v>
+      </c>
+      <c r="AA74">
+        <v>0</v>
+      </c>
+      <c r="AB74">
+        <v>7.72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>4</v>
+      </c>
+      <c r="B75">
+        <v>20251231</v>
+      </c>
+      <c r="C75">
+        <v>2</v>
+      </c>
+      <c r="D75">
+        <v>6.12</v>
+      </c>
+      <c r="E75">
+        <v>7.39</v>
+      </c>
+      <c r="F75">
+        <v>8.81</v>
+      </c>
+      <c r="G75">
+        <v>8.5</v>
+      </c>
+      <c r="H75">
+        <v>7.37</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>2.19</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>9.25</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>7.07</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="T75">
+        <v>6.2</v>
+      </c>
+      <c r="U75">
+        <v>8.33</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0</v>
+      </c>
+      <c r="X75">
+        <v>0</v>
+      </c>
+      <c r="Y75">
+        <v>8.17</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+      <c r="AA75">
+        <v>0</v>
+      </c>
+      <c r="AB75">
+        <v>5.07</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>5</v>
+      </c>
+      <c r="B76">
+        <v>20251231</v>
+      </c>
+      <c r="C76">
+        <v>2</v>
+      </c>
+      <c r="D76">
+        <v>7.32</v>
+      </c>
+      <c r="E76">
+        <v>7.49</v>
+      </c>
+      <c r="F76">
+        <v>10</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>9</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>8</v>
+      </c>
+      <c r="Q76">
+        <v>7.18</v>
+      </c>
+      <c r="R76">
+        <v>0</v>
+      </c>
+      <c r="S76">
+        <v>0</v>
+      </c>
+      <c r="T76">
+        <v>6.14</v>
+      </c>
+      <c r="U76">
+        <v>6.4</v>
+      </c>
+      <c r="V76">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="W76">
+        <v>0</v>
+      </c>
+      <c r="X76">
+        <v>0</v>
+      </c>
+      <c r="Y76">
+        <v>0</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+      <c r="AA76">
+        <v>0</v>
+      </c>
+      <c r="AB76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>6</v>
+      </c>
+      <c r="B77">
+        <v>20251231</v>
+      </c>
+      <c r="C77">
+        <v>2</v>
+      </c>
+      <c r="D77">
+        <v>6.6</v>
+      </c>
+      <c r="E77">
+        <v>7.5</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>9.4499999999999993</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>0</v>
+      </c>
+      <c r="R77">
+        <v>0</v>
+      </c>
+      <c r="S77">
+        <v>0</v>
+      </c>
+      <c r="T77">
+        <v>0</v>
+      </c>
+      <c r="U77">
+        <v>6</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0</v>
+      </c>
+      <c r="X77">
+        <v>0</v>
+      </c>
+      <c r="Y77">
+        <v>0</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+      <c r="AA77">
+        <v>0</v>
+      </c>
+      <c r="AB77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>7</v>
+      </c>
+      <c r="B78">
+        <v>20251231</v>
+      </c>
+      <c r="C78">
+        <v>2</v>
+      </c>
+      <c r="D78">
+        <v>7.95</v>
+      </c>
+      <c r="E78">
+        <v>8.27</v>
+      </c>
+      <c r="F78">
+        <v>7.41</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>8.85</v>
+      </c>
+      <c r="I78">
+        <v>6.5</v>
+      </c>
+      <c r="J78">
+        <v>4</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>2.77</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>4</v>
+      </c>
+      <c r="R78">
+        <v>0</v>
+      </c>
+      <c r="S78">
+        <v>0</v>
+      </c>
+      <c r="T78">
+        <v>4</v>
+      </c>
+      <c r="U78">
+        <v>8.01</v>
+      </c>
+      <c r="V78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>0</v>
+      </c>
+      <c r="X78">
+        <v>0</v>
+      </c>
+      <c r="Y78">
+        <v>8.1</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+      <c r="AA78">
+        <v>0</v>
+      </c>
+      <c r="AB78">
+        <v>7.58</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>8</v>
+      </c>
+      <c r="B79">
+        <v>20251231</v>
+      </c>
+      <c r="C79">
+        <v>2</v>
+      </c>
+      <c r="D79">
+        <v>5.5</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>5.5</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="R79">
+        <v>0</v>
+      </c>
+      <c r="S79">
+        <v>0</v>
+      </c>
+      <c r="T79">
+        <v>0</v>
+      </c>
+      <c r="U79">
+        <v>0</v>
+      </c>
+      <c r="V79">
+        <v>0</v>
+      </c>
+      <c r="W79">
+        <v>0</v>
+      </c>
+      <c r="X79">
+        <v>0</v>
+      </c>
+      <c r="Y79">
+        <v>0</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+      <c r="AA79">
+        <v>0</v>
+      </c>
+      <c r="AB79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>9</v>
+      </c>
+      <c r="B80">
+        <v>20251231</v>
+      </c>
+      <c r="C80">
+        <v>2</v>
+      </c>
+      <c r="D80">
+        <v>8.91</v>
+      </c>
+      <c r="E80">
+        <v>8.32</v>
+      </c>
+      <c r="F80">
+        <v>4.09</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>9.1</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>0</v>
+      </c>
+      <c r="R80">
+        <v>0</v>
+      </c>
+      <c r="S80">
+        <v>0</v>
+      </c>
+      <c r="T80">
+        <v>0</v>
+      </c>
+      <c r="U80">
+        <v>0</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>0</v>
+      </c>
+      <c r="X80">
+        <v>0</v>
+      </c>
+      <c r="Y80">
+        <v>9.07</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+      <c r="AA80">
+        <v>0</v>
+      </c>
+      <c r="AB80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>10</v>
+      </c>
+      <c r="B81">
+        <v>20251231</v>
+      </c>
+      <c r="C81">
+        <v>2</v>
+      </c>
+      <c r="D81">
         <v>8.8800000000000008</v>
       </c>
-      <c r="E69">
+      <c r="E81">
         <v>8.64</v>
       </c>
-      <c r="F69">
+      <c r="F81">
         <v>9.52</v>
       </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
-      <c r="H69">
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
         <v>9.2100000000000009</v>
       </c>
-      <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69">
-        <v>0</v>
-      </c>
-      <c r="K69">
-        <v>0</v>
-      </c>
-      <c r="L69">
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81">
         <v>6.5</v>
       </c>
-      <c r="M69">
-        <v>0</v>
-      </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
-      <c r="O69">
-        <v>0</v>
-      </c>
-      <c r="P69">
-        <v>0</v>
-      </c>
-      <c r="Q69">
-        <v>0</v>
-      </c>
-      <c r="R69">
-        <v>0</v>
-      </c>
-      <c r="S69">
-        <v>0</v>
-      </c>
-      <c r="T69">
-        <v>0</v>
-      </c>
-      <c r="U69">
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>0</v>
+      </c>
+      <c r="R81">
+        <v>0</v>
+      </c>
+      <c r="S81">
+        <v>0</v>
+      </c>
+      <c r="T81">
+        <v>0</v>
+      </c>
+      <c r="U81">
         <v>7.5</v>
       </c>
-      <c r="V69">
-        <v>0</v>
-      </c>
-      <c r="W69">
+      <c r="V81">
+        <v>0</v>
+      </c>
+      <c r="W81">
         <v>3.31</v>
       </c>
-      <c r="X69">
-        <v>0</v>
-      </c>
-      <c r="Y69">
+      <c r="X81">
+        <v>0</v>
+      </c>
+      <c r="Y81">
         <v>8.4600000000000009</v>
       </c>
-      <c r="Z69">
-        <v>0</v>
-      </c>
-      <c r="AA69">
-        <v>0</v>
-      </c>
-      <c r="AB69">
+      <c r="Z81">
+        <v>0</v>
+      </c>
+      <c r="AA81">
+        <v>0</v>
+      </c>
+      <c r="AB81">
         <v>0</v>
       </c>
     </row>
